--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DBC522-CD18-4D20-84CE-1C6D9C7EF9FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D4FDA0-1FB3-45AA-8A15-9CEE3CCCBF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="133">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -635,6 +635,15 @@
   </si>
   <si>
     <t>Reteta(id=2, 3 ingrediente)</t>
+  </si>
+  <si>
+    <t>F02. citirea unei liste de ingrediente valide</t>
+  </si>
+  <si>
+    <t>Trifan Alexandra-Isabela</t>
+  </si>
+  <si>
+    <t>Toda-Puiulet Emanuela-Coralia</t>
   </si>
 </sst>
 </file>
@@ -1440,173 +1449,204 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1620,40 +1660,9 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2674,12 +2683,12 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="37" t="s">
@@ -2726,8 +2735,12 @@
       <c r="N7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
+      <c r="O7" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="P7" s="25">
+        <v>237</v>
+      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
@@ -2737,8 +2750,12 @@
       <c r="N8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
+      <c r="O8" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="P8" s="25">
+        <v>237</v>
+      </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
@@ -2804,73 +2821,73 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="64"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="83"/>
+      <c r="B3" s="109" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="95"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="64"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="45"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
-      <c r="Q6" s="62" t="s">
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="Q6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="63"/>
-      <c r="S6" s="63"/>
-      <c r="T6" s="63"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="93" t="s">
+      <c r="C8" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="I8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="80" t="s">
+      <c r="Q8" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="80"/>
-      <c r="S8" s="80"/>
+      <c r="R8" s="97"/>
+      <c r="S8" s="97"/>
       <c r="T8" s="32">
         <v>6</v>
       </c>
@@ -2879,22 +2896,22 @@
       <c r="B9" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
       <c r="H9" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="I9" s="36"/>
-      <c r="Q9" s="80" t="s">
+      <c r="Q9" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="R9" s="80"/>
-      <c r="S9" s="80"/>
+      <c r="R9" s="97"/>
+      <c r="S9" s="97"/>
       <c r="T9" s="32" t="s">
         <v>81</v>
       </c>
@@ -2903,27 +2920,27 @@
       <c r="B10" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
       <c r="F10" s="34"/>
       <c r="G10" s="34"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="86"/>
-      <c r="Q10" s="80" t="s">
+      <c r="I10" s="83"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="85"/>
+      <c r="Q10" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="R10" s="80" t="s">
+      <c r="R10" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="S10" s="80"/>
+      <c r="S10" s="97"/>
       <c r="T10" s="32" t="s">
         <v>82</v>
       </c>
@@ -2932,502 +2949,512 @@
       <c r="B11" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="88"/>
-      <c r="K11" s="88"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="88"/>
-      <c r="O11" s="89"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
+      <c r="L11" s="87"/>
+      <c r="M11" s="87"/>
+      <c r="N11" s="87"/>
+      <c r="O11" s="88"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="88"/>
-      <c r="K12" s="88"/>
-      <c r="L12" s="88"/>
-      <c r="M12" s="88"/>
-      <c r="N12" s="88"/>
-      <c r="O12" s="89"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="87"/>
+      <c r="M12" s="87"/>
+      <c r="N12" s="87"/>
+      <c r="O12" s="88"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="88"/>
-      <c r="K13" s="88"/>
-      <c r="L13" s="88"/>
-      <c r="M13" s="88"/>
-      <c r="N13" s="88"/>
-      <c r="O13" s="89"/>
-      <c r="Q13" s="62" t="s">
+      <c r="I13" s="86"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="87"/>
+      <c r="M13" s="87"/>
+      <c r="N13" s="87"/>
+      <c r="O13" s="88"/>
+      <c r="Q13" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="R13" s="63"/>
-      <c r="S13" s="63"/>
-      <c r="T13" s="63"/>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="88"/>
-      <c r="N14" s="88"/>
-      <c r="O14" s="89"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
+      <c r="L14" s="87"/>
+      <c r="M14" s="87"/>
+      <c r="N14" s="87"/>
+      <c r="O14" s="88"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="87"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="89"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="87"/>
+      <c r="K15" s="87"/>
+      <c r="L15" s="87"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="87"/>
+      <c r="O15" s="88"/>
       <c r="Q15" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="R15" s="93" t="s">
+      <c r="R15" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="S15" s="93"/>
-      <c r="T15" s="93"/>
+      <c r="S15" s="98"/>
+      <c r="T15" s="98"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="87"/>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="88"/>
-      <c r="N16" s="88"/>
-      <c r="O16" s="89"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="87"/>
+      <c r="O16" s="88"/>
       <c r="Q16" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="R16" s="78" t="s">
+      <c r="R16" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="S16" s="78"/>
-      <c r="T16" s="78"/>
+      <c r="S16" s="99"/>
+      <c r="T16" s="99"/>
     </row>
     <row r="17" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I17" s="87"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="88"/>
-      <c r="N17" s="88"/>
-      <c r="O17" s="89"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="87"/>
+      <c r="N17" s="87"/>
+      <c r="O17" s="88"/>
       <c r="Q17" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="R17" s="78" t="s">
+      <c r="R17" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="S17" s="78"/>
-      <c r="T17" s="78"/>
+      <c r="S17" s="99"/>
+      <c r="T17" s="99"/>
     </row>
     <row r="18" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I18" s="87"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="88"/>
-      <c r="O18" s="89"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
+      <c r="O18" s="88"/>
       <c r="Q18" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="R18" s="78" t="s">
+      <c r="R18" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="S18" s="78"/>
-      <c r="T18" s="78"/>
+      <c r="S18" s="99"/>
+      <c r="T18" s="99"/>
     </row>
     <row r="19" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I19" s="87"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="89"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="87"/>
+      <c r="N19" s="87"/>
+      <c r="O19" s="88"/>
       <c r="Q19" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="R19" s="78" t="s">
+      <c r="R19" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="S19" s="78"/>
-      <c r="T19" s="78"/>
+      <c r="S19" s="99"/>
+      <c r="T19" s="99"/>
     </row>
     <row r="20" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I20" s="87"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="88"/>
-      <c r="N20" s="88"/>
-      <c r="O20" s="89"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="87"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="87"/>
+      <c r="M20" s="87"/>
+      <c r="N20" s="87"/>
+      <c r="O20" s="88"/>
       <c r="Q20" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="R20" s="103" t="s">
+      <c r="R20" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="S20" s="103"/>
-      <c r="T20" s="103"/>
+      <c r="S20" s="92"/>
+      <c r="T20" s="92"/>
     </row>
     <row r="21" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I21" s="87"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="88"/>
-      <c r="L21" s="88"/>
-      <c r="M21" s="88"/>
-      <c r="N21" s="88"/>
-      <c r="O21" s="89"/>
+      <c r="I21" s="86"/>
+      <c r="J21" s="87"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="87"/>
+      <c r="M21" s="87"/>
+      <c r="N21" s="87"/>
+      <c r="O21" s="88"/>
       <c r="Q21" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="R21" s="103" t="s">
+      <c r="R21" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="S21" s="103"/>
-      <c r="T21" s="103"/>
+      <c r="S21" s="92"/>
+      <c r="T21" s="92"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="87"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="88"/>
-      <c r="N22" s="88"/>
-      <c r="O22" s="89"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="87"/>
+      <c r="K22" s="87"/>
+      <c r="L22" s="87"/>
+      <c r="M22" s="87"/>
+      <c r="N22" s="87"/>
+      <c r="O22" s="88"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="87"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="88"/>
-      <c r="O23" s="89"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="87"/>
+      <c r="K23" s="87"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="87"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="88"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="90"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="92"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="91"/>
     </row>
     <row r="25" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I25" s="84"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="86"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="85"/>
     </row>
     <row r="26" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I26" s="87"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="88"/>
-      <c r="O26" s="89"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="87"/>
+      <c r="M26" s="87"/>
+      <c r="N26" s="87"/>
+      <c r="O26" s="88"/>
     </row>
     <row r="27" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I27" s="87"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="88"/>
-      <c r="O27" s="89"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="87"/>
+      <c r="L27" s="87"/>
+      <c r="M27" s="87"/>
+      <c r="N27" s="87"/>
+      <c r="O27" s="88"/>
     </row>
     <row r="28" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I28" s="87"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="88"/>
-      <c r="O28" s="89"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="87"/>
+      <c r="K28" s="87"/>
+      <c r="L28" s="87"/>
+      <c r="M28" s="87"/>
+      <c r="N28" s="87"/>
+      <c r="O28" s="88"/>
     </row>
     <row r="29" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I29" s="87"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="88"/>
-      <c r="N29" s="88"/>
-      <c r="O29" s="89"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="87"/>
+      <c r="L29" s="87"/>
+      <c r="M29" s="87"/>
+      <c r="N29" s="87"/>
+      <c r="O29" s="88"/>
     </row>
     <row r="30" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I30" s="87"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="88"/>
-      <c r="O30" s="89"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="87"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="87"/>
+      <c r="M30" s="87"/>
+      <c r="N30" s="87"/>
+      <c r="O30" s="88"/>
     </row>
     <row r="31" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I31" s="87"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="88"/>
-      <c r="N31" s="88"/>
-      <c r="O31" s="89"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="87"/>
+      <c r="M31" s="87"/>
+      <c r="N31" s="87"/>
+      <c r="O31" s="88"/>
     </row>
     <row r="32" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I32" s="87"/>
-      <c r="J32" s="88"/>
-      <c r="K32" s="88"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="88"/>
-      <c r="N32" s="88"/>
-      <c r="O32" s="89"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="87"/>
+      <c r="K32" s="87"/>
+      <c r="L32" s="87"/>
+      <c r="M32" s="87"/>
+      <c r="N32" s="87"/>
+      <c r="O32" s="88"/>
     </row>
     <row r="33" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I33" s="87"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
-      <c r="N33" s="88"/>
-      <c r="O33" s="89"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
+      <c r="L33" s="87"/>
+      <c r="M33" s="87"/>
+      <c r="N33" s="87"/>
+      <c r="O33" s="88"/>
     </row>
     <row r="34" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I34" s="87"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="89"/>
+      <c r="I34" s="86"/>
+      <c r="J34" s="87"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="87"/>
+      <c r="N34" s="87"/>
+      <c r="O34" s="88"/>
     </row>
     <row r="35" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I35" s="87"/>
-      <c r="J35" s="88"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="88"/>
-      <c r="M35" s="88"/>
-      <c r="N35" s="88"/>
-      <c r="O35" s="89"/>
+      <c r="I35" s="86"/>
+      <c r="J35" s="87"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="87"/>
+      <c r="M35" s="87"/>
+      <c r="N35" s="87"/>
+      <c r="O35" s="88"/>
     </row>
     <row r="36" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I36" s="87"/>
-      <c r="J36" s="88"/>
-      <c r="K36" s="88"/>
-      <c r="L36" s="88"/>
-      <c r="M36" s="88"/>
-      <c r="N36" s="88"/>
-      <c r="O36" s="89"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="87"/>
+      <c r="K36" s="87"/>
+      <c r="L36" s="87"/>
+      <c r="M36" s="87"/>
+      <c r="N36" s="87"/>
+      <c r="O36" s="88"/>
     </row>
     <row r="37" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I37" s="87"/>
-      <c r="J37" s="88"/>
-      <c r="K37" s="88"/>
-      <c r="L37" s="88"/>
-      <c r="M37" s="88"/>
-      <c r="N37" s="88"/>
-      <c r="O37" s="89"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="87"/>
+      <c r="K37" s="87"/>
+      <c r="L37" s="87"/>
+      <c r="M37" s="87"/>
+      <c r="N37" s="87"/>
+      <c r="O37" s="88"/>
     </row>
     <row r="38" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I38" s="87"/>
-      <c r="J38" s="88"/>
-      <c r="K38" s="88"/>
-      <c r="L38" s="88"/>
-      <c r="M38" s="88"/>
-      <c r="N38" s="88"/>
-      <c r="O38" s="89"/>
+      <c r="I38" s="86"/>
+      <c r="J38" s="87"/>
+      <c r="K38" s="87"/>
+      <c r="L38" s="87"/>
+      <c r="M38" s="87"/>
+      <c r="N38" s="87"/>
+      <c r="O38" s="88"/>
     </row>
     <row r="39" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I39" s="90"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
-      <c r="M39" s="91"/>
-      <c r="N39" s="91"/>
-      <c r="O39" s="92"/>
+      <c r="I39" s="89"/>
+      <c r="J39" s="90"/>
+      <c r="K39" s="90"/>
+      <c r="L39" s="90"/>
+      <c r="M39" s="90"/>
+      <c r="N39" s="90"/>
+      <c r="O39" s="91"/>
     </row>
     <row r="40" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I40" s="84"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="85"/>
-      <c r="L40" s="85"/>
-      <c r="M40" s="85"/>
-      <c r="N40" s="85"/>
-      <c r="O40" s="86"/>
+      <c r="I40" s="83"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
+      <c r="O40" s="85"/>
     </row>
     <row r="41" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I41" s="87"/>
-      <c r="J41" s="88"/>
-      <c r="K41" s="88"/>
-      <c r="L41" s="88"/>
-      <c r="M41" s="88"/>
-      <c r="N41" s="88"/>
-      <c r="O41" s="89"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="87"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="87"/>
+      <c r="M41" s="87"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="88"/>
     </row>
     <row r="42" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I42" s="87"/>
-      <c r="J42" s="88"/>
-      <c r="K42" s="88"/>
-      <c r="L42" s="88"/>
-      <c r="M42" s="88"/>
-      <c r="N42" s="88"/>
-      <c r="O42" s="89"/>
+      <c r="I42" s="86"/>
+      <c r="J42" s="87"/>
+      <c r="K42" s="87"/>
+      <c r="L42" s="87"/>
+      <c r="M42" s="87"/>
+      <c r="N42" s="87"/>
+      <c r="O42" s="88"/>
     </row>
     <row r="43" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I43" s="87"/>
-      <c r="J43" s="88"/>
-      <c r="K43" s="88"/>
-      <c r="L43" s="88"/>
-      <c r="M43" s="88"/>
-      <c r="N43" s="88"/>
-      <c r="O43" s="89"/>
+      <c r="I43" s="86"/>
+      <c r="J43" s="87"/>
+      <c r="K43" s="87"/>
+      <c r="L43" s="87"/>
+      <c r="M43" s="87"/>
+      <c r="N43" s="87"/>
+      <c r="O43" s="88"/>
     </row>
     <row r="44" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I44" s="87"/>
-      <c r="J44" s="88"/>
-      <c r="K44" s="88"/>
-      <c r="L44" s="88"/>
-      <c r="M44" s="88"/>
-      <c r="N44" s="88"/>
-      <c r="O44" s="89"/>
+      <c r="I44" s="86"/>
+      <c r="J44" s="87"/>
+      <c r="K44" s="87"/>
+      <c r="L44" s="87"/>
+      <c r="M44" s="87"/>
+      <c r="N44" s="87"/>
+      <c r="O44" s="88"/>
     </row>
     <row r="45" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I45" s="87"/>
-      <c r="J45" s="88"/>
-      <c r="K45" s="88"/>
-      <c r="L45" s="88"/>
-      <c r="M45" s="88"/>
-      <c r="N45" s="88"/>
-      <c r="O45" s="89"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="87"/>
+      <c r="K45" s="87"/>
+      <c r="L45" s="87"/>
+      <c r="M45" s="87"/>
+      <c r="N45" s="87"/>
+      <c r="O45" s="88"/>
     </row>
     <row r="46" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I46" s="87"/>
-      <c r="J46" s="88"/>
-      <c r="K46" s="88"/>
-      <c r="L46" s="88"/>
-      <c r="M46" s="88"/>
-      <c r="N46" s="88"/>
-      <c r="O46" s="89"/>
+      <c r="I46" s="86"/>
+      <c r="J46" s="87"/>
+      <c r="K46" s="87"/>
+      <c r="L46" s="87"/>
+      <c r="M46" s="87"/>
+      <c r="N46" s="87"/>
+      <c r="O46" s="88"/>
     </row>
     <row r="47" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I47" s="87"/>
-      <c r="J47" s="88"/>
-      <c r="K47" s="88"/>
-      <c r="L47" s="88"/>
-      <c r="M47" s="88"/>
-      <c r="N47" s="88"/>
-      <c r="O47" s="89"/>
+      <c r="I47" s="86"/>
+      <c r="J47" s="87"/>
+      <c r="K47" s="87"/>
+      <c r="L47" s="87"/>
+      <c r="M47" s="87"/>
+      <c r="N47" s="87"/>
+      <c r="O47" s="88"/>
     </row>
     <row r="48" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I48" s="87"/>
-      <c r="J48" s="88"/>
-      <c r="K48" s="88"/>
-      <c r="L48" s="88"/>
-      <c r="M48" s="88"/>
-      <c r="N48" s="88"/>
-      <c r="O48" s="89"/>
+      <c r="I48" s="86"/>
+      <c r="J48" s="87"/>
+      <c r="K48" s="87"/>
+      <c r="L48" s="87"/>
+      <c r="M48" s="87"/>
+      <c r="N48" s="87"/>
+      <c r="O48" s="88"/>
     </row>
     <row r="49" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I49" s="87"/>
-      <c r="J49" s="88"/>
-      <c r="K49" s="88"/>
-      <c r="L49" s="88"/>
-      <c r="M49" s="88"/>
-      <c r="N49" s="88"/>
-      <c r="O49" s="89"/>
+      <c r="I49" s="86"/>
+      <c r="J49" s="87"/>
+      <c r="K49" s="87"/>
+      <c r="L49" s="87"/>
+      <c r="M49" s="87"/>
+      <c r="N49" s="87"/>
+      <c r="O49" s="88"/>
     </row>
     <row r="50" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I50" s="87"/>
-      <c r="J50" s="88"/>
-      <c r="K50" s="88"/>
-      <c r="L50" s="88"/>
-      <c r="M50" s="88"/>
-      <c r="N50" s="88"/>
-      <c r="O50" s="89"/>
+      <c r="I50" s="86"/>
+      <c r="J50" s="87"/>
+      <c r="K50" s="87"/>
+      <c r="L50" s="87"/>
+      <c r="M50" s="87"/>
+      <c r="N50" s="87"/>
+      <c r="O50" s="88"/>
     </row>
     <row r="51" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I51" s="87"/>
-      <c r="J51" s="88"/>
-      <c r="K51" s="88"/>
-      <c r="L51" s="88"/>
-      <c r="M51" s="88"/>
-      <c r="N51" s="88"/>
-      <c r="O51" s="89"/>
+      <c r="I51" s="86"/>
+      <c r="J51" s="87"/>
+      <c r="K51" s="87"/>
+      <c r="L51" s="87"/>
+      <c r="M51" s="87"/>
+      <c r="N51" s="87"/>
+      <c r="O51" s="88"/>
     </row>
     <row r="52" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I52" s="87"/>
-      <c r="J52" s="88"/>
-      <c r="K52" s="88"/>
-      <c r="L52" s="88"/>
-      <c r="M52" s="88"/>
-      <c r="N52" s="88"/>
-      <c r="O52" s="89"/>
+      <c r="I52" s="86"/>
+      <c r="J52" s="87"/>
+      <c r="K52" s="87"/>
+      <c r="L52" s="87"/>
+      <c r="M52" s="87"/>
+      <c r="N52" s="87"/>
+      <c r="O52" s="88"/>
     </row>
     <row r="53" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I53" s="87"/>
-      <c r="J53" s="88"/>
-      <c r="K53" s="88"/>
-      <c r="L53" s="88"/>
-      <c r="M53" s="88"/>
-      <c r="N53" s="88"/>
-      <c r="O53" s="89"/>
+      <c r="I53" s="86"/>
+      <c r="J53" s="87"/>
+      <c r="K53" s="87"/>
+      <c r="L53" s="87"/>
+      <c r="M53" s="87"/>
+      <c r="N53" s="87"/>
+      <c r="O53" s="88"/>
     </row>
     <row r="54" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I54" s="90"/>
-      <c r="J54" s="91"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="91"/>
-      <c r="M54" s="91"/>
-      <c r="N54" s="91"/>
-      <c r="O54" s="92"/>
+      <c r="I54" s="89"/>
+      <c r="J54" s="90"/>
+      <c r="K54" s="90"/>
+      <c r="L54" s="90"/>
+      <c r="M54" s="90"/>
+      <c r="N54" s="90"/>
+      <c r="O54" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="I25:O39"/>
     <mergeCell ref="I40:O54"/>
     <mergeCell ref="D1:I1"/>
@@ -3444,16 +3471,6 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="I6:O6"/>
     <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3486,21 +3503,21 @@
   <sheetData>
     <row r="1" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="83"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="95"/>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B5" s="9"/>
@@ -3546,113 +3563,113 @@
       <c r="B7" s="100"/>
       <c r="C7" s="100"/>
       <c r="D7" s="102"/>
-      <c r="E7" s="97" t="s">
+      <c r="E7" s="108" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="96" t="s">
+      <c r="F7" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
-      <c r="M7" s="96"/>
-      <c r="N7" s="96"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="98" t="s">
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" s="98"/>
-      <c r="R7" s="98"/>
-      <c r="S7" s="98"/>
-      <c r="T7" s="98"/>
-      <c r="U7" s="98"/>
-      <c r="V7" s="99" t="s">
+      <c r="Q7" s="104"/>
+      <c r="R7" s="104"/>
+      <c r="S7" s="104"/>
+      <c r="T7" s="104"/>
+      <c r="U7" s="104"/>
+      <c r="V7" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="W7" s="99"/>
-      <c r="X7" s="99"/>
-      <c r="Y7" s="99"/>
-      <c r="Z7" s="99"/>
-      <c r="AA7" s="99"/>
-      <c r="AB7" s="99"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="103"/>
+      <c r="Y7" s="103"/>
+      <c r="Z7" s="103"/>
+      <c r="AA7" s="103"/>
+      <c r="AB7" s="103"/>
     </row>
     <row r="8" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="100"/>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="94" t="s">
+      <c r="D8" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="97"/>
-      <c r="F8" s="96" t="s">
+      <c r="E8" s="108"/>
+      <c r="F8" s="107" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96" t="s">
+      <c r="G8" s="107"/>
+      <c r="H8" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96" t="s">
+      <c r="I8" s="107"/>
+      <c r="J8" s="107" t="s">
         <v>94</v>
       </c>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96" t="s">
+      <c r="K8" s="107"/>
+      <c r="L8" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96" t="s">
+      <c r="M8" s="107"/>
+      <c r="N8" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="O8" s="96"/>
-      <c r="P8" s="98" t="s">
+      <c r="O8" s="107"/>
+      <c r="P8" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="Q8" s="98" t="s">
+      <c r="Q8" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="R8" s="98" t="s">
+      <c r="R8" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="S8" s="98" t="s">
+      <c r="S8" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="T8" s="98" t="s">
+      <c r="T8" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="U8" s="98" t="s">
+      <c r="U8" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="V8" s="99">
+      <c r="V8" s="103">
         <v>0</v>
       </c>
-      <c r="W8" s="99">
+      <c r="W8" s="103">
         <v>1</v>
       </c>
-      <c r="X8" s="99">
+      <c r="X8" s="103">
         <v>2</v>
       </c>
-      <c r="Y8" s="99" t="s">
+      <c r="Y8" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="Z8" s="99" t="s">
+      <c r="Z8" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="AA8" s="99" t="s">
+      <c r="AA8" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="AB8" s="99" t="s">
+      <c r="AB8" s="103" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="100"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="97"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="108"/>
       <c r="F9" s="11" t="s">
         <v>50</v>
       </c>
@@ -3683,21 +3700,21 @@
       <c r="O9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="98"/>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="99"/>
-      <c r="X9" s="99"/>
-      <c r="Y9" s="99"/>
-      <c r="Z9" s="99"/>
-      <c r="AA9" s="99"/>
-      <c r="AB9" s="99"/>
-    </row>
-    <row r="10" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="P9" s="104"/>
+      <c r="Q9" s="104"/>
+      <c r="R9" s="104"/>
+      <c r="S9" s="104"/>
+      <c r="T9" s="104"/>
+      <c r="U9" s="104"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="103"/>
+      <c r="Z9" s="103"/>
+      <c r="AA9" s="103"/>
+      <c r="AB9" s="103"/>
+    </row>
+    <row r="10" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="12" t="s">
         <v>52</v>
       </c>
@@ -3781,7 +3798,7 @@
       <c r="AA11" s="17"/>
       <c r="AB11" s="17"/>
     </row>
-    <row r="12" spans="2:28" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B12" s="12" t="s">
         <v>97</v>
       </c>
@@ -3987,7 +4004,7 @@
       <c r="D16" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="104" t="s">
+      <c r="E16" s="38" t="s">
         <v>119</v>
       </c>
       <c r="F16" s="15" t="s">
@@ -4032,6 +4049,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="P7:U7"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
@@ -4048,20 +4079,6 @@
     <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:U7"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4093,55 +4110,55 @@
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="62" t="s">
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="64"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="68" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="L4" s="69"/>
+      <c r="L4" s="50"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="67"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="77"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="59"/>
       <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
@@ -4152,10 +4169,10 @@
       <c r="H5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="I5" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="71"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="2" t="s">
         <v>60</v>
       </c>
@@ -4167,7 +4184,7 @@
       <c r="B6" s="20">
         <v>9</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="53" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -4185,10 +4202,10 @@
       <c r="H6" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="107" t="s">
+      <c r="I6" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="108"/>
+      <c r="J6" s="61"/>
       <c r="K6" s="21" t="s">
         <v>109</v>
       </c>
@@ -4200,7 +4217,7 @@
       <c r="B7" s="20">
         <v>10</v>
       </c>
-      <c r="C7" s="72"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="4" t="s">
         <v>63</v>
       </c>
@@ -4216,10 +4233,10 @@
       <c r="H7" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="68" t="s">
+      <c r="I7" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="69"/>
+      <c r="J7" s="50"/>
       <c r="K7" s="21" t="s">
         <v>109</v>
       </c>
@@ -4231,7 +4248,7 @@
       <c r="B8" s="20">
         <v>11</v>
       </c>
-      <c r="C8" s="72"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="4" t="s">
         <v>122</v>
       </c>
@@ -4247,10 +4264,10 @@
       <c r="H8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="68" t="s">
+      <c r="I8" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="69"/>
+      <c r="J8" s="50"/>
       <c r="K8" s="20" t="s">
         <v>110</v>
       </c>
@@ -4262,7 +4279,7 @@
       <c r="B9" s="20">
         <v>12</v>
       </c>
-      <c r="C9" s="72"/>
+      <c r="C9" s="53"/>
       <c r="D9" s="4" t="s">
         <v>123</v>
       </c>
@@ -4278,10 +4295,10 @@
       <c r="H9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="68" t="s">
+      <c r="I9" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="69"/>
+      <c r="J9" s="50"/>
       <c r="K9" s="20" t="s">
         <v>110</v>
       </c>
@@ -4293,7 +4310,7 @@
       <c r="B10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="73"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="4" t="s">
         <v>124</v>
       </c>
@@ -4309,10 +4326,10 @@
       <c r="H10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="70" t="s">
+      <c r="I10" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="71"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="20" t="s">
         <v>110</v>
       </c>
@@ -4321,8 +4338,8 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="105"/>
-      <c r="C11" s="106"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="39"/>
       <c r="D11" s="4" t="s">
         <v>125</v>
       </c>
@@ -4338,18 +4355,18 @@
       <c r="H11" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105" t="s">
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="L11" s="105" t="s">
+      <c r="L11" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="105"/>
-      <c r="C12" s="106"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="4" t="s">
         <v>126</v>
       </c>
@@ -4365,27 +4382,27 @@
       <c r="H12" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105" t="s">
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="L12" s="105" t="s">
+      <c r="L12" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="3"/>
@@ -4407,83 +4424,83 @@
       <c r="K15" s="22"/>
     </row>
     <row r="16" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="46" t="s">
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="47"/>
-      <c r="H16" s="54" t="s">
+      <c r="G16" s="63"/>
+      <c r="H16" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="60" t="s">
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="N16" s="61"/>
+      <c r="N16" s="78"/>
     </row>
     <row r="17" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="F17" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="48" t="s">
+      <c r="G17" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="50" t="s">
+      <c r="H17" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="40" t="s">
+      <c r="J17" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="K17" s="52" t="s">
+      <c r="K17" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="L17" s="57" t="s">
+      <c r="L17" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="M17" s="59" t="s">
+      <c r="M17" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="N17" s="49" t="s">
+      <c r="N17" s="56" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="39"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="44"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="74"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="65"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="25">
@@ -4495,7 +4512,7 @@
       <c r="D19" s="23">
         <v>0</v>
       </c>
-      <c r="E19" s="109">
+      <c r="E19" s="40">
         <v>0.8</v>
       </c>
       <c r="F19" s="24"/>
@@ -4526,6 +4543,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="J17:J18"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:L3"/>
@@ -4542,21 +4574,6 @@
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="F16:G16"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4565,14 +4582,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4765,21 +4780,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4804,9 +4818,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D4FDA0-1FB3-45AA-8A15-9CEE3CCCBF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4ECCC8F-DE61-45F9-A907-7E122BFCF248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="131">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -91,55 +91,7 @@
     <t>Student 2:</t>
   </si>
   <si>
-    <t>1. Evidenţa filmelor din colecţia personală</t>
-  </si>
-  <si>
     <t>Student 3:</t>
-  </si>
-  <si>
-    <t>Un cinefil doreşte să îşi dezvolte un program pentru gestionarea filmelor din colecţia personală. Programul va permite următoarele operaţii:</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>F02.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> cautarea filmelor care au un anumit regizor (sau parti din numele regizorului);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">F02. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cautarea filmelor care au un anumit regizor (sau parti din numele regizorului).</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">F02. Covered source code </t>
@@ -644,6 +596,30 @@
   </si>
   <si>
     <t>Toda-Puiulet Emanuela-Coralia</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">F02. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>citirea unei liste de ingrediente valide</t>
+    </r>
+  </si>
+  <si>
+    <t>1. citirea unei liste de ingrediente valide</t>
   </si>
 </sst>
 </file>
@@ -1456,20 +1432,161 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1501,9 +1618,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1524,144 +1638,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2683,12 +2659,12 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="37" t="s">
@@ -2736,7 +2712,7 @@
         <v>9</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P7" s="25">
         <v>237</v>
@@ -2751,7 +2727,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="P8" s="25">
         <v>237</v>
@@ -2759,28 +2735,25 @@
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="N9" s="25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O9" s="25"/>
       <c r="P9" s="25"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="35" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -2821,640 +2794,630 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="45"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="109" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
-      <c r="I3" s="94"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="95"/>
+      <c r="B3" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="59"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45"/>
+      <c r="B6" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="43"/>
       <c r="F6" s="29"/>
       <c r="G6" s="29"/>
-      <c r="I6" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="Q6" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
+      <c r="I6" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="Q6" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="98" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
+        <v>15</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="I8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8" s="97" t="s">
-        <v>22</v>
-      </c>
-      <c r="R8" s="97"/>
-      <c r="S8" s="97"/>
+        <v>17</v>
+      </c>
+      <c r="Q8" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
       <c r="T8" s="32">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
+        <v>20</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
       <c r="F9" s="34"/>
       <c r="G9" s="34"/>
       <c r="H9" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="I9" s="36"/>
-      <c r="Q9" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="R9" s="97"/>
-      <c r="S9" s="97"/>
+      <c r="Q9" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
       <c r="T9" s="32" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
+        <v>22</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
       <c r="F10" s="34"/>
       <c r="G10" s="34"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84"/>
-      <c r="M10" s="84"/>
-      <c r="N10" s="84"/>
-      <c r="O10" s="85"/>
-      <c r="Q10" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="S10" s="97"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="49"/>
+      <c r="Q10" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="S10" s="46"/>
       <c r="T10" s="32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B11" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
+        <v>25</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
       <c r="F11" s="34"/>
       <c r="G11" s="34"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="87"/>
-      <c r="L11" s="87"/>
-      <c r="M11" s="87"/>
-      <c r="N11" s="87"/>
-      <c r="O11" s="88"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="52"/>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
+        <v>26</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
       <c r="F12" s="34"/>
       <c r="G12" s="34"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="87"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="87"/>
-      <c r="M12" s="87"/>
-      <c r="N12" s="87"/>
-      <c r="O12" s="88"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="52"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
+        <v>27</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="87"/>
-      <c r="L13" s="87"/>
-      <c r="M13" s="87"/>
-      <c r="N13" s="87"/>
-      <c r="O13" s="88"/>
-      <c r="Q13" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="52"/>
+      <c r="Q13" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B14" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="96" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
+        <v>26</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
-      <c r="N14" s="87"/>
-      <c r="O14" s="88"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="52"/>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I15" s="86"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="87"/>
-      <c r="L15" s="87"/>
-      <c r="M15" s="87"/>
-      <c r="N15" s="87"/>
-      <c r="O15" s="88"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="52"/>
       <c r="Q15" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="S15" s="60"/>
+      <c r="T15" s="60"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I16" s="50"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="52"/>
+      <c r="Q16" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
+    </row>
+    <row r="17" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I17" s="50"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="51"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="52"/>
+      <c r="Q17" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="S17" s="44"/>
+      <c r="T17" s="44"/>
+    </row>
+    <row r="18" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I18" s="50"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="51"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="52"/>
+      <c r="Q18" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="R15" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" s="98"/>
-      <c r="T15" s="98"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I16" s="86"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="87"/>
-      <c r="N16" s="87"/>
-      <c r="O16" s="88"/>
-      <c r="Q16" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="R16" s="99" t="s">
+      <c r="R18" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="S18" s="44"/>
+      <c r="T18" s="44"/>
+    </row>
+    <row r="19" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I19" s="50"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="52"/>
+      <c r="Q19" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="R19" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
+    </row>
+    <row r="20" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I20" s="50"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="52"/>
+      <c r="Q20" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="S16" s="99"/>
-      <c r="T16" s="99"/>
-    </row>
-    <row r="17" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I17" s="86"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="87"/>
-      <c r="L17" s="87"/>
-      <c r="M17" s="87"/>
-      <c r="N17" s="87"/>
-      <c r="O17" s="88"/>
-      <c r="Q17" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="R17" s="99" t="s">
+      <c r="R20" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="S20" s="56"/>
+      <c r="T20" s="56"/>
+    </row>
+    <row r="21" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I21" s="50"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="52"/>
+      <c r="Q21" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="S17" s="99"/>
-      <c r="T17" s="99"/>
-    </row>
-    <row r="18" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I18" s="86"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="87"/>
-      <c r="L18" s="87"/>
-      <c r="M18" s="87"/>
-      <c r="N18" s="87"/>
-      <c r="O18" s="88"/>
-      <c r="Q18" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="R18" s="99" t="s">
-        <v>85</v>
-      </c>
-      <c r="S18" s="99"/>
-      <c r="T18" s="99"/>
-    </row>
-    <row r="19" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I19" s="86"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="87"/>
-      <c r="N19" s="87"/>
-      <c r="O19" s="88"/>
-      <c r="Q19" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="R19" s="99" t="s">
-        <v>89</v>
-      </c>
-      <c r="S19" s="99"/>
-      <c r="T19" s="99"/>
-    </row>
-    <row r="20" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I20" s="86"/>
-      <c r="J20" s="87"/>
-      <c r="K20" s="87"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="87"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="88"/>
-      <c r="Q20" s="33" t="s">
+      <c r="R21" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="R20" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="S20" s="92"/>
-      <c r="T20" s="92"/>
-    </row>
-    <row r="21" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I21" s="86"/>
-      <c r="J21" s="87"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="87"/>
-      <c r="N21" s="87"/>
-      <c r="O21" s="88"/>
-      <c r="Q21" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="R21" s="92" t="s">
-        <v>91</v>
-      </c>
-      <c r="S21" s="92"/>
-      <c r="T21" s="92"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="56"/>
     </row>
     <row r="22" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="86"/>
-      <c r="J22" s="87"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="87"/>
-      <c r="M22" s="87"/>
-      <c r="N22" s="87"/>
-      <c r="O22" s="88"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="52"/>
     </row>
     <row r="23" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="86"/>
-      <c r="J23" s="87"/>
-      <c r="K23" s="87"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="87"/>
-      <c r="N23" s="87"/>
-      <c r="O23" s="88"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="52"/>
     </row>
     <row r="24" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="89"/>
-      <c r="J24" s="90"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="91"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="55"/>
     </row>
     <row r="25" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I25" s="83"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="84"/>
-      <c r="M25" s="84"/>
-      <c r="N25" s="84"/>
-      <c r="O25" s="85"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="49"/>
     </row>
     <row r="26" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I26" s="86"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="87"/>
-      <c r="N26" s="87"/>
-      <c r="O26" s="88"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="52"/>
     </row>
     <row r="27" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I27" s="86"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="88"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="51"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="52"/>
     </row>
     <row r="28" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I28" s="86"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="87"/>
-      <c r="O28" s="88"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="52"/>
     </row>
     <row r="29" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I29" s="86"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="87"/>
-      <c r="N29" s="87"/>
-      <c r="O29" s="88"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="51"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="52"/>
     </row>
     <row r="30" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I30" s="86"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="87"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="88"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+      <c r="L30" s="51"/>
+      <c r="M30" s="51"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="52"/>
     </row>
     <row r="31" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I31" s="86"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="87"/>
-      <c r="N31" s="87"/>
-      <c r="O31" s="88"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="52"/>
     </row>
     <row r="32" spans="9:20" x14ac:dyDescent="0.3">
-      <c r="I32" s="86"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="87"/>
-      <c r="N32" s="87"/>
-      <c r="O32" s="88"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="51"/>
+      <c r="M32" s="51"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="52"/>
     </row>
     <row r="33" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I33" s="86"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87"/>
-      <c r="N33" s="87"/>
-      <c r="O33" s="88"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="51"/>
+      <c r="M33" s="51"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="52"/>
     </row>
     <row r="34" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I34" s="86"/>
-      <c r="J34" s="87"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="87"/>
-      <c r="N34" s="87"/>
-      <c r="O34" s="88"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="51"/>
+      <c r="L34" s="51"/>
+      <c r="M34" s="51"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="52"/>
     </row>
     <row r="35" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I35" s="86"/>
-      <c r="J35" s="87"/>
-      <c r="K35" s="87"/>
-      <c r="L35" s="87"/>
-      <c r="M35" s="87"/>
-      <c r="N35" s="87"/>
-      <c r="O35" s="88"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="51"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="52"/>
     </row>
     <row r="36" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I36" s="86"/>
-      <c r="J36" s="87"/>
-      <c r="K36" s="87"/>
-      <c r="L36" s="87"/>
-      <c r="M36" s="87"/>
-      <c r="N36" s="87"/>
-      <c r="O36" s="88"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="52"/>
     </row>
     <row r="37" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I37" s="86"/>
-      <c r="J37" s="87"/>
-      <c r="K37" s="87"/>
-      <c r="L37" s="87"/>
-      <c r="M37" s="87"/>
-      <c r="N37" s="87"/>
-      <c r="O37" s="88"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="51"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="51"/>
+      <c r="O37" s="52"/>
     </row>
     <row r="38" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I38" s="86"/>
-      <c r="J38" s="87"/>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="87"/>
-      <c r="N38" s="87"/>
-      <c r="O38" s="88"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="51"/>
+      <c r="M38" s="51"/>
+      <c r="N38" s="51"/>
+      <c r="O38" s="52"/>
     </row>
     <row r="39" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I39" s="89"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90"/>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
-      <c r="N39" s="90"/>
-      <c r="O39" s="91"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="54"/>
+      <c r="N39" s="54"/>
+      <c r="O39" s="55"/>
     </row>
     <row r="40" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I40" s="83"/>
-      <c r="J40" s="84"/>
-      <c r="K40" s="84"/>
-      <c r="L40" s="84"/>
-      <c r="M40" s="84"/>
-      <c r="N40" s="84"/>
-      <c r="O40" s="85"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
+      <c r="M40" s="48"/>
+      <c r="N40" s="48"/>
+      <c r="O40" s="49"/>
     </row>
     <row r="41" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I41" s="86"/>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
-      <c r="N41" s="87"/>
-      <c r="O41" s="88"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+      <c r="L41" s="51"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="51"/>
+      <c r="O41" s="52"/>
     </row>
     <row r="42" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I42" s="86"/>
-      <c r="J42" s="87"/>
-      <c r="K42" s="87"/>
-      <c r="L42" s="87"/>
-      <c r="M42" s="87"/>
-      <c r="N42" s="87"/>
-      <c r="O42" s="88"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="51"/>
+      <c r="M42" s="51"/>
+      <c r="N42" s="51"/>
+      <c r="O42" s="52"/>
     </row>
     <row r="43" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I43" s="86"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="87"/>
-      <c r="L43" s="87"/>
-      <c r="M43" s="87"/>
-      <c r="N43" s="87"/>
-      <c r="O43" s="88"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="51"/>
+      <c r="K43" s="51"/>
+      <c r="L43" s="51"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="51"/>
+      <c r="O43" s="52"/>
     </row>
     <row r="44" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I44" s="86"/>
-      <c r="J44" s="87"/>
-      <c r="K44" s="87"/>
-      <c r="L44" s="87"/>
-      <c r="M44" s="87"/>
-      <c r="N44" s="87"/>
-      <c r="O44" s="88"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="51"/>
+      <c r="L44" s="51"/>
+      <c r="M44" s="51"/>
+      <c r="N44" s="51"/>
+      <c r="O44" s="52"/>
     </row>
     <row r="45" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I45" s="86"/>
-      <c r="J45" s="87"/>
-      <c r="K45" s="87"/>
-      <c r="L45" s="87"/>
-      <c r="M45" s="87"/>
-      <c r="N45" s="87"/>
-      <c r="O45" s="88"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+      <c r="L45" s="51"/>
+      <c r="M45" s="51"/>
+      <c r="N45" s="51"/>
+      <c r="O45" s="52"/>
     </row>
     <row r="46" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I46" s="86"/>
-      <c r="J46" s="87"/>
-      <c r="K46" s="87"/>
-      <c r="L46" s="87"/>
-      <c r="M46" s="87"/>
-      <c r="N46" s="87"/>
-      <c r="O46" s="88"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="51"/>
+      <c r="K46" s="51"/>
+      <c r="L46" s="51"/>
+      <c r="M46" s="51"/>
+      <c r="N46" s="51"/>
+      <c r="O46" s="52"/>
     </row>
     <row r="47" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I47" s="86"/>
-      <c r="J47" s="87"/>
-      <c r="K47" s="87"/>
-      <c r="L47" s="87"/>
-      <c r="M47" s="87"/>
-      <c r="N47" s="87"/>
-      <c r="O47" s="88"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="51"/>
+      <c r="K47" s="51"/>
+      <c r="L47" s="51"/>
+      <c r="M47" s="51"/>
+      <c r="N47" s="51"/>
+      <c r="O47" s="52"/>
     </row>
     <row r="48" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I48" s="86"/>
-      <c r="J48" s="87"/>
-      <c r="K48" s="87"/>
-      <c r="L48" s="87"/>
-      <c r="M48" s="87"/>
-      <c r="N48" s="87"/>
-      <c r="O48" s="88"/>
+      <c r="I48" s="50"/>
+      <c r="J48" s="51"/>
+      <c r="K48" s="51"/>
+      <c r="L48" s="51"/>
+      <c r="M48" s="51"/>
+      <c r="N48" s="51"/>
+      <c r="O48" s="52"/>
     </row>
     <row r="49" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I49" s="86"/>
-      <c r="J49" s="87"/>
-      <c r="K49" s="87"/>
-      <c r="L49" s="87"/>
-      <c r="M49" s="87"/>
-      <c r="N49" s="87"/>
-      <c r="O49" s="88"/>
+      <c r="I49" s="50"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="51"/>
+      <c r="L49" s="51"/>
+      <c r="M49" s="51"/>
+      <c r="N49" s="51"/>
+      <c r="O49" s="52"/>
     </row>
     <row r="50" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I50" s="86"/>
-      <c r="J50" s="87"/>
-      <c r="K50" s="87"/>
-      <c r="L50" s="87"/>
-      <c r="M50" s="87"/>
-      <c r="N50" s="87"/>
-      <c r="O50" s="88"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="51"/>
+      <c r="L50" s="51"/>
+      <c r="M50" s="51"/>
+      <c r="N50" s="51"/>
+      <c r="O50" s="52"/>
     </row>
     <row r="51" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I51" s="86"/>
-      <c r="J51" s="87"/>
-      <c r="K51" s="87"/>
-      <c r="L51" s="87"/>
-      <c r="M51" s="87"/>
-      <c r="N51" s="87"/>
-      <c r="O51" s="88"/>
+      <c r="I51" s="50"/>
+      <c r="J51" s="51"/>
+      <c r="K51" s="51"/>
+      <c r="L51" s="51"/>
+      <c r="M51" s="51"/>
+      <c r="N51" s="51"/>
+      <c r="O51" s="52"/>
     </row>
     <row r="52" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I52" s="86"/>
-      <c r="J52" s="87"/>
-      <c r="K52" s="87"/>
-      <c r="L52" s="87"/>
-      <c r="M52" s="87"/>
-      <c r="N52" s="87"/>
-      <c r="O52" s="88"/>
+      <c r="I52" s="50"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="51"/>
+      <c r="L52" s="51"/>
+      <c r="M52" s="51"/>
+      <c r="N52" s="51"/>
+      <c r="O52" s="52"/>
     </row>
     <row r="53" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I53" s="86"/>
-      <c r="J53" s="87"/>
-      <c r="K53" s="87"/>
-      <c r="L53" s="87"/>
-      <c r="M53" s="87"/>
-      <c r="N53" s="87"/>
-      <c r="O53" s="88"/>
+      <c r="I53" s="50"/>
+      <c r="J53" s="51"/>
+      <c r="K53" s="51"/>
+      <c r="L53" s="51"/>
+      <c r="M53" s="51"/>
+      <c r="N53" s="51"/>
+      <c r="O53" s="52"/>
     </row>
     <row r="54" spans="9:15" x14ac:dyDescent="0.3">
-      <c r="I54" s="89"/>
-      <c r="J54" s="90"/>
-      <c r="K54" s="90"/>
-      <c r="L54" s="90"/>
-      <c r="M54" s="90"/>
-      <c r="N54" s="90"/>
-      <c r="O54" s="91"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="54"/>
+      <c r="O54" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="I25:O39"/>
     <mergeCell ref="I40:O54"/>
     <mergeCell ref="D1:I1"/>
@@ -3471,6 +3434,16 @@
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="I6:O6"/>
     <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3503,232 +3476,232 @@
   <sheetData>
     <row r="1" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B3" s="93" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="95"/>
+      <c r="B3" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="59"/>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B5" s="9"/>
     </row>
     <row r="6" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="68"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="68"/>
+      <c r="U6" s="68"/>
+      <c r="V6" s="68"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="68"/>
+      <c r="Y6" s="68"/>
+      <c r="Z6" s="68"/>
+      <c r="AA6" s="68"/>
+      <c r="AB6" s="68"/>
+    </row>
+    <row r="7" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="100" t="s">
+      <c r="F7" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="101" t="s">
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="100" t="s">
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="65"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="100"/>
-      <c r="L6" s="100"/>
-      <c r="M6" s="100"/>
-      <c r="N6" s="100"/>
-      <c r="O6" s="100"/>
-      <c r="P6" s="100"/>
-      <c r="Q6" s="100"/>
-      <c r="R6" s="100"/>
-      <c r="S6" s="100"/>
-      <c r="T6" s="100"/>
-      <c r="U6" s="100"/>
-      <c r="V6" s="100"/>
-      <c r="W6" s="100"/>
-      <c r="X6" s="100"/>
-      <c r="Y6" s="100"/>
-      <c r="Z6" s="100"/>
-      <c r="AA6" s="100"/>
-      <c r="AB6" s="100"/>
-    </row>
-    <row r="7" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="108" t="s">
+      <c r="W7" s="66"/>
+      <c r="X7" s="66"/>
+      <c r="Y7" s="66"/>
+      <c r="Z7" s="66"/>
+      <c r="AA7" s="66"/>
+      <c r="AB7" s="66"/>
+    </row>
+    <row r="8" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="68"/>
+      <c r="C8" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="64"/>
+      <c r="F8" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="O8" s="63"/>
+      <c r="P8" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="U8" s="65" t="s">
+        <v>84</v>
+      </c>
+      <c r="V8" s="66">
+        <v>0</v>
+      </c>
+      <c r="W8" s="66">
+        <v>1</v>
+      </c>
+      <c r="X8" s="66">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="107" t="s">
+      <c r="Z8" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="104" t="s">
+      <c r="AA8" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="104"/>
-      <c r="S7" s="104"/>
-      <c r="T7" s="104"/>
-      <c r="U7" s="104"/>
-      <c r="V7" s="103" t="s">
+      <c r="AB8" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="W7" s="103"/>
-      <c r="X7" s="103"/>
-      <c r="Y7" s="103"/>
-      <c r="Z7" s="103"/>
-      <c r="AA7" s="103"/>
-      <c r="AB7" s="103"/>
-    </row>
-    <row r="8" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="100"/>
-      <c r="C8" s="105" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="105" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="108"/>
-      <c r="F8" s="107" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="107"/>
-      <c r="J8" s="107" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" s="107"/>
-      <c r="L8" s="107" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" s="107"/>
-      <c r="N8" s="107" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="107"/>
-      <c r="P8" s="104" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" s="104" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" s="104" t="s">
-        <v>37</v>
-      </c>
-      <c r="S8" s="104" t="s">
-        <v>86</v>
-      </c>
-      <c r="T8" s="104" t="s">
-        <v>87</v>
-      </c>
-      <c r="U8" s="104" t="s">
-        <v>88</v>
-      </c>
-      <c r="V8" s="103">
-        <v>0</v>
-      </c>
-      <c r="W8" s="103">
-        <v>1</v>
-      </c>
-      <c r="X8" s="103">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="103" t="s">
+    </row>
+    <row r="9" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="68"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="Z8" s="103" t="s">
+      <c r="G9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AA8" s="103" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB8" s="103" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="100"/>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="H9" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="104"/>
-      <c r="S9" s="104"/>
-      <c r="T9" s="104"/>
-      <c r="U9" s="104"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103"/>
-      <c r="Y9" s="103"/>
-      <c r="Z9" s="103"/>
-      <c r="AA9" s="103"/>
-      <c r="AB9" s="103"/>
+        <v>47</v>
+      </c>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="65"/>
+      <c r="U9" s="65"/>
+      <c r="V9" s="66"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="66"/>
+      <c r="Y9" s="66"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="66"/>
     </row>
     <row r="10" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E10" s="14">
         <v>1</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
@@ -3740,7 +3713,7 @@
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
       <c r="P10" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
@@ -3757,19 +3730,19 @@
     </row>
     <row r="11" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B11" s="12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E11" s="14">
         <v>1</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
@@ -3781,7 +3754,7 @@
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
       <c r="P11" s="16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
@@ -3789,7 +3762,7 @@
       <c r="T11" s="16"/>
       <c r="U11" s="16"/>
       <c r="V11" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="W11" s="17"/>
       <c r="X11" s="17"/>
@@ -3800,23 +3773,23 @@
     </row>
     <row r="12" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B12" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="15"/>
@@ -3827,7 +3800,7 @@
       <c r="O12" s="15"/>
       <c r="P12" s="16"/>
       <c r="Q12" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
@@ -3843,27 +3816,27 @@
     </row>
     <row r="13" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B13" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G13" s="15"/>
       <c r="H13" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
@@ -3874,13 +3847,13 @@
       <c r="Q13" s="16"/>
       <c r="R13" s="16"/>
       <c r="S13" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
       <c r="V13" s="17"/>
       <c r="W13" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="X13" s="17"/>
       <c r="Y13" s="17"/>
@@ -3890,35 +3863,35 @@
     </row>
     <row r="14" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B14" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O14" s="15"/>
       <c r="P14" s="16"/>
@@ -3926,14 +3899,14 @@
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
       <c r="T14" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="U14" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="V14" s="17"/>
       <c r="W14" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="X14" s="17"/>
       <c r="Y14" s="17"/>
@@ -3943,38 +3916,38 @@
     </row>
     <row r="15" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P15" s="16"/>
       <c r="Q15" s="16"/>
@@ -3982,11 +3955,11 @@
       <c r="S15" s="16"/>
       <c r="T15" s="16"/>
       <c r="U15" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="V15" s="17"/>
       <c r="W15" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="X15" s="17"/>
       <c r="Y15" s="17"/>
@@ -3996,38 +3969,38 @@
     </row>
     <row r="16" spans="2:28" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B16" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L16" s="15"/>
       <c r="M16" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P16" s="16"/>
       <c r="Q16" s="16"/>
@@ -4035,34 +4008,20 @@
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
       <c r="U16" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="V16" s="17"/>
       <c r="W16" s="17"/>
       <c r="X16" s="17"/>
       <c r="Y16" s="17"/>
       <c r="Z16" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="AA16" s="17"/>
       <c r="AB16" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:U7"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
@@ -4079,6 +4038,20 @@
     <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="V7:AB7"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="P7:U7"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4110,285 +4083,285 @@
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="93" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="94" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="47" t="s">
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" s="50"/>
+      <c r="L4" s="97"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="48"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="59"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="105"/>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="52"/>
+        <v>19</v>
+      </c>
+      <c r="I5" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="99"/>
       <c r="K5" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="20">
         <v>9</v>
       </c>
-      <c r="C6" s="53" t="s">
-        <v>62</v>
+      <c r="C6" s="100" t="s">
+        <v>58</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="60" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="61"/>
+        <v>19</v>
+      </c>
+      <c r="I6" s="106" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="107"/>
       <c r="K6" s="21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="20">
         <v>10</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="100"/>
       <c r="D7" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="50"/>
+        <v>19</v>
+      </c>
+      <c r="I7" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="97"/>
       <c r="K7" s="21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="20">
         <v>11</v>
       </c>
-      <c r="C8" s="53"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="50"/>
+        <v>19</v>
+      </c>
+      <c r="I8" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="97"/>
       <c r="K8" s="20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="20">
         <v>12</v>
       </c>
-      <c r="C9" s="53"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="50"/>
+        <v>19</v>
+      </c>
+      <c r="I9" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="97"/>
       <c r="K9" s="20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="54"/>
+      <c r="C10" s="101"/>
       <c r="D10" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E10" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="98" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="99"/>
+      <c r="K10" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="52"/>
-      <c r="K10" s="20" t="s">
-        <v>110</v>
-      </c>
       <c r="L10" s="20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="39"/>
       <c r="D11" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="39"/>
       <c r="D12" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
@@ -4419,88 +4392,88 @@
     </row>
     <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K15" s="22"/>
+    </row>
+    <row r="16" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="108" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="109"/>
+      <c r="H16" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="22"/>
-    </row>
-    <row r="16" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="41" t="s">
+      <c r="N16" s="79"/>
+    </row>
+    <row r="17" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="62" t="s">
+      <c r="C17" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="63"/>
-      <c r="H16" s="41" t="s">
+      <c r="D17" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="77" t="s">
+      <c r="E17" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="N16" s="78"/>
-    </row>
-    <row r="17" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="76" t="s">
+      <c r="F17" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="68" t="s">
+      <c r="G17" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="68" t="s">
+      <c r="H17" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="80" t="s">
+      <c r="I17" s="81" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="K17" s="91" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="65" t="s">
+      <c r="L17" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="M17" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="66" t="s">
+      <c r="N17" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="68" t="s">
-        <v>69</v>
-      </c>
-      <c r="J17" s="68" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="L17" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="M17" s="75" t="s">
-        <v>78</v>
-      </c>
-      <c r="N17" s="56" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="79"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="65"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="77"/>
+      <c r="N18" s="85"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="25">
@@ -4517,10 +4490,10 @@
       </c>
       <c r="F19" s="24"/>
       <c r="G19" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I19" s="25">
         <f>SUM(J19:K19)</f>
@@ -4534,7 +4507,7 @@
       </c>
       <c r="L19" s="27"/>
       <c r="M19" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N19" s="28">
         <f>C19</f>
@@ -4543,6 +4516,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="H16:L16"/>
     <mergeCell ref="L17:L18"/>
     <mergeCell ref="M17:M18"/>
@@ -4559,21 +4547,6 @@
     <mergeCell ref="K17:K18"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C6:C10"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F16:G16"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4582,12 +4555,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4780,20 +4755,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4818,12 +4794,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>